--- a/docs/sprint3/execution-log.xlsx
+++ b/docs/sprint3/execution-log.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Сторінка номера не завантажується: запит GET /api/room/{id} повертає 500, на сторінці лишається індикатор завантаження. Кейс неможливо довести до кроку, що перевіряється</t>
+          <t>Крок 3: після натискання «Book now» відкривається /reservation/1?checkin=2026-10-28&amp;checkout=2026-10-29. Крок 4: вміст сторінки не з'являється, лишається індикатор завантаження; GET /api/room/1 повертає 500, тип номера, правила заїзду і «Price Summary» не показано</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026 14:00–18:30 EET</t>
+          <t>28.10.2026 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>30.10.2026, 14:00–18:30 EET</t>
+          <t>28.10.2026, 15:30–20:00 EET</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Повідомлення, надіслане о 14:05, зникло до 14:20; повторне надсилання збереглося. Результат перевіряти одразу після дії</t>
+          <t>Повідомлення, надіслане о 16:05, зникло до 16:20; повторне надсилання збереглося. Результат перевіряти одразу після дії</t>
         </is>
       </c>
     </row>
@@ -2600,11 +2600,11 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Для кожного failed створено звіт про дефект</t>
+          <t>Для кожного failed-кейсу створено звіт про дефект</t>
         </is>
       </c>
     </row>
@@ -2615,11 +2615,11 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Заблоковані дефектом BUG-001 (сторінка номера не відкривається)</t>
+          <t>TC-013 … TC-017: сторінку номера не відкрито через BUG-001, кейс неможливо довести до кроку, що перевіряється</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Blocker, Major, Normal, Minor, Trivial</t>
+          <t>Critical, Major, Normal, Minor, Trivial</t>
         </is>
       </c>
     </row>
